--- a/Sounds.xlsx
+++ b/Sounds.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/623821e34d642ca0/Desktop/ASVGC-25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{8189D8F4-1E64-4DF1-B2A6-68F1B77D596A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DF9B04D-50FD-45D8-8FEE-A3DEC9958ADF}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{8189D8F4-1E64-4DF1-B2A6-68F1B77D596A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0875F7D-48A9-4C0A-A146-AD34622D5D66}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{53BCC81A-2A92-4691-9841-E4BA723E9FDD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>URL</t>
   </si>
@@ -56,10 +56,43 @@
     <t xml:space="preserve">https://freesound.org/people/AugustSandberg/sounds/264864/ </t>
   </si>
   <si>
-    <t>Boat engine 3</t>
-  </si>
-  <si>
-    <t>Marine diesel engine by AugustSandberg -- https://freesound.org/s/264864/ -- License: Creative Commons 0</t>
+    <t>https://freesound.org/people/F.M.Audio/sounds/620830/</t>
+  </si>
+  <si>
+    <t>CC-BY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://freesound.org/s/264864/ </t>
+  </si>
+  <si>
+    <t>Low Metal Thud 2.wav by F.M.Audio -- License: Attribution 4.0</t>
+  </si>
+  <si>
+    <t>Marine diesel engine by AugustSandberg -- License: Creative Commons 0</t>
+  </si>
+  <si>
+    <t>https://freesound.org/s/620830/</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Low Metal Thud (in the dmg sound)</t>
+  </si>
+  <si>
+    <t>Marine Disel Engine (in the player bote)</t>
+  </si>
+  <si>
+    <t>https://freesound.org/people/Benboncan/sounds/84111/</t>
+  </si>
+  <si>
+    <t>Wind</t>
+  </si>
+  <si>
+    <t>Wind On Door Short.wav by Benboncan  -- License: Attribution 4.0</t>
+  </si>
+  <si>
+    <t>https://freesound.org/s/84111/</t>
   </si>
 </sst>
 </file>
@@ -473,14 +506,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAFFBA9D-9989-4AF2-B6F6-460B4EA90217}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" customWidth="1"/>
     <col min="2" max="2" width="35.6640625" customWidth="1"/>
     <col min="3" max="3" width="65.5546875" customWidth="1"/>
-    <col min="4" max="4" width="161.88671875" customWidth="1"/>
-    <col min="5" max="5" width="61.33203125" customWidth="1"/>
+    <col min="4" max="4" width="88.44140625" customWidth="1"/>
+    <col min="5" max="5" width="52.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -496,27 +529,63 @@
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C3" s="2"/>
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:A1048576 A1:A3">
+  <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="CC-BY-NC">
       <formula>NOT(ISERROR(SEARCH("CC-BY-NC",A1)))</formula>
     </cfRule>
@@ -529,6 +598,8 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{435F98E6-A5DA-4910-A772-3DC6D6D53A7E}"/>
+    <hyperlink ref="C3" r:id="rId2" tooltip="https://freesound.org/people/F.M.Audio/sounds/620830/" xr:uid="{C5B6E2F8-A0DC-484D-880D-75131719CAB8}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{69FF51DC-8DAC-49A3-B169-588A7D4BF72A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
